--- a/Results/nested_cv_results_with_95CI.xlsx
+++ b/Results/nested_cv_results_with_95CI.xlsx
@@ -14,69 +14,75 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="32">
   <si>
     <t>Model</t>
   </si>
   <si>
-    <t>accuracy_mean</t>
-  </si>
-  <si>
-    <t>accuracy_sd</t>
-  </si>
-  <si>
-    <t>accuracy_ci_low</t>
-  </si>
-  <si>
-    <t>accuracy_ci_high</t>
-  </si>
-  <si>
-    <t>precision_mean</t>
-  </si>
-  <si>
-    <t>precision_sd</t>
-  </si>
-  <si>
-    <t>precision_ci_low</t>
-  </si>
-  <si>
-    <t>precision_ci_high</t>
-  </si>
-  <si>
-    <t>recall_mean</t>
-  </si>
-  <si>
-    <t>recall_sd</t>
-  </si>
-  <si>
-    <t>recall_ci_low</t>
-  </si>
-  <si>
-    <t>recall_ci_high</t>
-  </si>
-  <si>
-    <t>f1_mean</t>
-  </si>
-  <si>
-    <t>f1_sd</t>
-  </si>
-  <si>
-    <t>f1_ci_low</t>
-  </si>
-  <si>
-    <t>f1_ci_high</t>
-  </si>
-  <si>
-    <t>roc_auc_mean</t>
-  </si>
-  <si>
-    <t>roc_auc_sd</t>
-  </si>
-  <si>
-    <t>roc_auc_ci_low</t>
-  </si>
-  <si>
-    <t>roc_auc_ci_high</t>
+    <t>N_outer_scores</t>
+  </si>
+  <si>
+    <t>CI_interpretation</t>
+  </si>
+  <si>
+    <t>Accuracy_mean</t>
+  </si>
+  <si>
+    <t>Accuracy_sd</t>
+  </si>
+  <si>
+    <t>Accuracy_CI_lower</t>
+  </si>
+  <si>
+    <t>Accuracy_CI_upper</t>
+  </si>
+  <si>
+    <t>Precision_mean</t>
+  </si>
+  <si>
+    <t>Precision_sd</t>
+  </si>
+  <si>
+    <t>Precision_CI_lower</t>
+  </si>
+  <si>
+    <t>Precision_CI_upper</t>
+  </si>
+  <si>
+    <t>Recall_mean</t>
+  </si>
+  <si>
+    <t>Recall_sd</t>
+  </si>
+  <si>
+    <t>Recall_CI_lower</t>
+  </si>
+  <si>
+    <t>Recall_CI_upper</t>
+  </si>
+  <si>
+    <t>F1_mean</t>
+  </si>
+  <si>
+    <t>F1_sd</t>
+  </si>
+  <si>
+    <t>F1_CI_lower</t>
+  </si>
+  <si>
+    <t>F1_CI_upper</t>
+  </si>
+  <si>
+    <t>ROC_AUC_mean</t>
+  </si>
+  <si>
+    <t>ROC_AUC_sd</t>
+  </si>
+  <si>
+    <t>ROC_AUC_CI_lower</t>
+  </si>
+  <si>
+    <t>ROC_AUC_CI_upper</t>
   </si>
   <si>
     <t>Logistic Regression</t>
@@ -101,6 +107,9 @@
   </si>
   <si>
     <t>XGBoost</t>
+  </si>
+  <si>
+    <t>descriptive fold-resampling interval; correlated folds</t>
   </si>
 </sst>
 </file>
@@ -458,10 +467,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U9"/>
+  <dimension ref="A1:W9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:21">
+    <row r="1" spans="1:23">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -525,525 +534,579 @@
       <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="2" spans="1:21">
+    <row r="2" spans="1:23">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B2">
-        <v>0.7909292854498334</v>
-      </c>
-      <c r="C2">
-        <v>0.04357977161242459</v>
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>31</v>
       </c>
       <c r="D2">
-        <v>0.7597541948654909</v>
+        <v>0.8345454545454546</v>
       </c>
       <c r="E2">
-        <v>0.822104376034176</v>
+        <v>0.03368955662954492</v>
       </c>
       <c r="F2">
-        <v>0.8076255670699976</v>
+        <v>0.8104453975508243</v>
       </c>
       <c r="G2">
-        <v>0.05420716680876481</v>
+        <v>0.8586455115400848</v>
       </c>
       <c r="H2">
-        <v>0.7688480959392857</v>
+        <v>0.8482380138289525</v>
       </c>
       <c r="I2">
-        <v>0.8464030382007094</v>
+        <v>0.05292850259831471</v>
       </c>
       <c r="J2">
-        <v>0.8188414634146343</v>
+        <v>0.8103752439716263</v>
       </c>
       <c r="K2">
-        <v>0.05473139845281892</v>
+        <v>0.8861007836862786</v>
       </c>
       <c r="L2">
-        <v>0.7796889795570107</v>
+        <v>0.8616129032258065</v>
       </c>
       <c r="M2">
-        <v>0.8579939472722579</v>
+        <v>0.06371273982023237</v>
       </c>
       <c r="N2">
-        <v>0.8116371091066128</v>
+        <v>0.816035554795965</v>
       </c>
       <c r="O2">
-        <v>0.03969820346146467</v>
+        <v>0.907190251655648</v>
       </c>
       <c r="P2">
-        <v>0.7832387251051238</v>
+        <v>0.8520301362406089</v>
       </c>
       <c r="Q2">
-        <v>0.8400354931081018</v>
+        <v>0.02804986846246906</v>
       </c>
       <c r="R2">
-        <v>0.863131005173688</v>
+        <v>0.8319644691239171</v>
       </c>
       <c r="S2">
-        <v>0.02932350644092644</v>
+        <v>0.8720958033573006</v>
       </c>
       <c r="T2">
-        <v>0.8421542323333777</v>
+        <v>0.9215559139784946</v>
       </c>
       <c r="U2">
-        <v>0.8841077780139983</v>
+        <v>0.02512010642220828</v>
+      </c>
+      <c r="V2">
+        <v>0.9035860723702058</v>
+      </c>
+      <c r="W2">
+        <v>0.9395257555867833</v>
       </c>
     </row>
-    <row r="3" spans="1:21">
+    <row r="3" spans="1:23">
       <c r="A3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B3">
-        <v>0.7923546834505739</v>
-      </c>
-      <c r="C3">
-        <v>0.0327044083336016</v>
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>31</v>
       </c>
       <c r="D3">
-        <v>0.7689593590928694</v>
+        <v>0.8309090909090908</v>
       </c>
       <c r="E3">
-        <v>0.8157500078082784</v>
+        <v>0.04457739526892916</v>
       </c>
       <c r="F3">
-        <v>0.8168946304199883</v>
+        <v>0.7990203433524904</v>
       </c>
       <c r="G3">
-        <v>0.04492051536734913</v>
+        <v>0.8627978384656912</v>
       </c>
       <c r="H3">
-        <v>0.7847604295313998</v>
+        <v>0.8373620026614038</v>
       </c>
       <c r="I3">
-        <v>0.8490288313085769</v>
+        <v>0.05789608511294951</v>
       </c>
       <c r="J3">
-        <v>0.8064634146341463</v>
+        <v>0.7959456383461667</v>
       </c>
       <c r="K3">
-        <v>0.05188877502148436</v>
+        <v>0.8787783669766409</v>
       </c>
       <c r="L3">
-        <v>0.7693444210792522</v>
+        <v>0.8680645161290321</v>
       </c>
       <c r="M3">
-        <v>0.8435824081890404</v>
+        <v>0.06754736807703883</v>
       </c>
       <c r="N3">
-        <v>0.8101685133110179</v>
+        <v>0.8197440398937861</v>
       </c>
       <c r="O3">
-        <v>0.03102887772910575</v>
+        <v>0.9163849923642782</v>
       </c>
       <c r="P3">
-        <v>0.7879717913424343</v>
+        <v>0.8500617253340519</v>
       </c>
       <c r="Q3">
-        <v>0.8323652352796015</v>
+        <v>0.04002206669336524</v>
       </c>
       <c r="R3">
-        <v>0.8611744733924611</v>
+        <v>0.8214316635330271</v>
       </c>
       <c r="S3">
-        <v>0.02723901571440763</v>
+        <v>0.8786917871350767</v>
       </c>
       <c r="T3">
-        <v>0.8416888553888346</v>
+        <v>0.8901682795698926</v>
       </c>
       <c r="U3">
-        <v>0.8806600913960876</v>
+        <v>0.04656032527303933</v>
+      </c>
+      <c r="V3">
+        <v>0.8568610293407605</v>
+      </c>
+      <c r="W3">
+        <v>0.9234755297990248</v>
       </c>
     </row>
-    <row r="4" spans="1:21">
+    <row r="4" spans="1:23">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B4">
-        <v>0.7923546834505738</v>
-      </c>
-      <c r="C4">
-        <v>0.04732264291005808</v>
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>31</v>
       </c>
       <c r="D4">
-        <v>0.7585021040352437</v>
+        <v>0.8309090909090908</v>
       </c>
       <c r="E4">
-        <v>0.826207262865904</v>
+        <v>0.03325058599841258</v>
       </c>
       <c r="F4">
-        <v>0.7931221902117246</v>
+        <v>0.8071230545869672</v>
       </c>
       <c r="G4">
-        <v>0.0383424446074394</v>
+        <v>0.8546951272312144</v>
       </c>
       <c r="H4">
-        <v>0.7656936576693174</v>
+        <v>0.8471615970575599</v>
       </c>
       <c r="I4">
-        <v>0.8205507227541318</v>
+        <v>0.04614553258026435</v>
       </c>
       <c r="J4">
-        <v>0.8438414634146343</v>
+        <v>0.8141510716457578</v>
       </c>
       <c r="K4">
-        <v>0.07735145914507729</v>
+        <v>0.8801721224693619</v>
       </c>
       <c r="L4">
-        <v>0.7885075629269283</v>
+        <v>0.8519354838709677</v>
       </c>
       <c r="M4">
-        <v>0.8991753639023403</v>
+        <v>0.04135414844930541</v>
       </c>
       <c r="N4">
-        <v>0.8161746896503477</v>
+        <v>0.8223525081864901</v>
       </c>
       <c r="O4">
-        <v>0.04699709434424937</v>
+        <v>0.8815184595554454</v>
       </c>
       <c r="P4">
-        <v>0.7825549936498033</v>
+        <v>0.8482007451121678</v>
       </c>
       <c r="Q4">
-        <v>0.849794385650892</v>
+        <v>0.0259894034644776</v>
       </c>
       <c r="R4">
-        <v>0.8714033628972653</v>
+        <v>0.8296090458613364</v>
       </c>
       <c r="S4">
-        <v>0.02900220394339588</v>
+        <v>0.8667924443629992</v>
       </c>
       <c r="T4">
-        <v>0.8506564360174748</v>
+        <v>0.911668817204301</v>
       </c>
       <c r="U4">
-        <v>0.8921502897770558</v>
+        <v>0.02833720489804787</v>
+      </c>
+      <c r="V4">
+        <v>0.8913976019840759</v>
+      </c>
+      <c r="W4">
+        <v>0.9319400324245262</v>
       </c>
     </row>
-    <row r="5" spans="1:21">
+    <row r="5" spans="1:23">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B5">
-        <v>0.7868752313957794</v>
-      </c>
-      <c r="C5">
-        <v>0.05041399735121611</v>
+        <v>10</v>
+      </c>
+      <c r="C5" t="s">
+        <v>31</v>
       </c>
       <c r="D5">
-        <v>0.7508112302321091</v>
+        <v>0.8054545454545454</v>
       </c>
       <c r="E5">
-        <v>0.8229392325594498</v>
+        <v>0.02275755558244675</v>
       </c>
       <c r="F5">
-        <v>0.777921839120463</v>
+        <v>0.7891747709052286</v>
       </c>
       <c r="G5">
-        <v>0.06033726671123925</v>
+        <v>0.8217343200038623</v>
       </c>
       <c r="H5">
-        <v>0.7347591586901177</v>
+        <v>0.8243225049803996</v>
       </c>
       <c r="I5">
-        <v>0.8210845195508083</v>
+        <v>0.04086346498470764</v>
       </c>
       <c r="J5">
-        <v>0.8684146341463416</v>
+        <v>0.7950905431009763</v>
       </c>
       <c r="K5">
-        <v>0.07904168150348613</v>
+        <v>0.8535544668598229</v>
       </c>
       <c r="L5">
-        <v>0.811871621421892</v>
+        <v>0.8313978494623656</v>
       </c>
       <c r="M5">
-        <v>0.9249576468707912</v>
+        <v>0.08830423985562789</v>
       </c>
       <c r="N5">
-        <v>0.8173464701014925</v>
+        <v>0.7682288016535914</v>
       </c>
       <c r="O5">
-        <v>0.04424602641261999</v>
+        <v>0.8945668972711398</v>
       </c>
       <c r="P5">
-        <v>0.7856947695446823</v>
+        <v>0.8237031629945329</v>
       </c>
       <c r="Q5">
-        <v>0.8489981706583027</v>
+        <v>0.03013441977020702</v>
       </c>
       <c r="R5">
-        <v>0.8372096729490023</v>
+        <v>0.8021462977039637</v>
       </c>
       <c r="S5">
-        <v>0.05314108780159359</v>
+        <v>0.8452600282851022</v>
       </c>
       <c r="T5">
-        <v>0.7991948287983995</v>
+        <v>0.8869397849462366</v>
       </c>
       <c r="U5">
-        <v>0.875224517099605</v>
+        <v>0.03517804888552743</v>
+      </c>
+      <c r="V5">
+        <v>0.8617749247367791</v>
+      </c>
+      <c r="W5">
+        <v>0.9121046451556941</v>
       </c>
     </row>
-    <row r="6" spans="1:21">
+    <row r="6" spans="1:23">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B6">
-        <v>0.8059237319511293</v>
-      </c>
-      <c r="C6">
-        <v>0.05862813589917309</v>
+        <v>10</v>
+      </c>
+      <c r="C6" t="s">
+        <v>31</v>
       </c>
       <c r="D6">
-        <v>0.763983690050433</v>
+        <v>0.8363636363636363</v>
       </c>
       <c r="E6">
-        <v>0.8478637738518257</v>
+        <v>0.03206971286138894</v>
       </c>
       <c r="F6">
-        <v>0.7927632633146734</v>
+        <v>0.8134223457951787</v>
       </c>
       <c r="G6">
-        <v>0.06322557690785566</v>
+        <v>0.8593049269320939</v>
       </c>
       <c r="H6">
-        <v>0.7475344102385419</v>
+        <v>0.8385646436725851</v>
       </c>
       <c r="I6">
-        <v>0.8379921163908048</v>
+        <v>0.04611553585967371</v>
       </c>
       <c r="J6">
-        <v>0.8834146341463416</v>
+        <v>0.8055755766220145</v>
       </c>
       <c r="K6">
-        <v>0.05998573210398697</v>
+        <v>0.8715537107231557</v>
       </c>
       <c r="L6">
-        <v>0.840503426424988</v>
+        <v>0.8780645161290324</v>
       </c>
       <c r="M6">
-        <v>0.9263258418676952</v>
+        <v>0.05793427581075319</v>
       </c>
       <c r="N6">
-        <v>0.8340567538625688</v>
+        <v>0.8366208318343769</v>
       </c>
       <c r="O6">
-        <v>0.0490642579053245</v>
+        <v>0.9195082004236879</v>
       </c>
       <c r="P6">
-        <v>0.7989582981328019</v>
+        <v>0.8557545832607062</v>
       </c>
       <c r="Q6">
-        <v>0.8691552095923357</v>
+        <v>0.02755191127836468</v>
       </c>
       <c r="R6">
-        <v>0.8819766260162603</v>
+        <v>0.83604513325455</v>
       </c>
       <c r="S6">
-        <v>0.02928849721447083</v>
+        <v>0.8754640332668624</v>
       </c>
       <c r="T6">
-        <v>0.8610248972678682</v>
+        <v>0.9184645161290323</v>
       </c>
       <c r="U6">
-        <v>0.9029283547646523</v>
+        <v>0.03010805759900904</v>
+      </c>
+      <c r="V6">
+        <v>0.8969265091996865</v>
+      </c>
+      <c r="W6">
+        <v>0.9400025230583782</v>
       </c>
     </row>
-    <row r="7" spans="1:21">
+    <row r="7" spans="1:23">
       <c r="A7" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B7">
-        <v>0.8004813032210292</v>
-      </c>
-      <c r="C7">
-        <v>0.0422269552842026</v>
+        <v>10</v>
+      </c>
+      <c r="C7" t="s">
+        <v>31</v>
       </c>
       <c r="D7">
-        <v>0.7702739591396141</v>
+        <v>0.8472727272727273</v>
       </c>
       <c r="E7">
-        <v>0.8306886473024443</v>
+        <v>0.03656509849454143</v>
       </c>
       <c r="F7">
-        <v>0.8116883394458675</v>
+        <v>0.8211156315465132</v>
       </c>
       <c r="G7">
-        <v>0.04985156417799723</v>
+        <v>0.8734298229989413</v>
       </c>
       <c r="H7">
-        <v>0.7760266787368162</v>
+        <v>0.8671485501073933</v>
       </c>
       <c r="I7">
-        <v>0.8473500001549188</v>
+        <v>0.06686095919555668</v>
       </c>
       <c r="J7">
-        <v>0.833719512195122</v>
+        <v>0.8193191012058473</v>
       </c>
       <c r="K7">
-        <v>0.05229785782397212</v>
+        <v>0.9149779990089394</v>
       </c>
       <c r="L7">
-        <v>0.7963078784323472</v>
+        <v>0.8648387096774194</v>
       </c>
       <c r="M7">
-        <v>0.8711311459578968</v>
+        <v>0.05694538561413257</v>
       </c>
       <c r="N7">
-        <v>0.821321164846518</v>
+        <v>0.8241024348141806</v>
       </c>
       <c r="O7">
-        <v>0.0384806935645654</v>
+        <v>0.9055749845406582</v>
       </c>
       <c r="P7">
-        <v>0.793793734957885</v>
+        <v>0.8628564973736148</v>
       </c>
       <c r="Q7">
-        <v>0.848848594735151</v>
+        <v>0.02861307397450134</v>
       </c>
       <c r="R7">
-        <v>0.8637342941611234</v>
+        <v>0.8423879373044</v>
       </c>
       <c r="S7">
-        <v>0.02974996777479775</v>
+        <v>0.8833250574428296</v>
       </c>
       <c r="T7">
-        <v>0.8424524492604912</v>
+        <v>0.9221021505376343</v>
       </c>
       <c r="U7">
-        <v>0.8850161390617555</v>
+        <v>0.02478248289590625</v>
+      </c>
+      <c r="V7">
+        <v>0.9043738302505099</v>
+      </c>
+      <c r="W7">
+        <v>0.9398304708247588</v>
       </c>
     </row>
-    <row r="8" spans="1:21">
+    <row r="8" spans="1:23">
       <c r="A8" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B8">
-        <v>0.8114587189929656</v>
-      </c>
-      <c r="C8">
-        <v>0.04992365354409589</v>
+        <v>10</v>
+      </c>
+      <c r="C8" t="s">
+        <v>31</v>
       </c>
       <c r="D8">
-        <v>0.7757454886580274</v>
+        <v>0.8418181818181818</v>
       </c>
       <c r="E8">
-        <v>0.8471719493279039</v>
+        <v>0.03096252066532069</v>
       </c>
       <c r="F8">
-        <v>0.8104303446319705</v>
+        <v>0.8196689288334379</v>
       </c>
       <c r="G8">
-        <v>0.05588450354255491</v>
+        <v>0.8639674348029257</v>
       </c>
       <c r="H8">
-        <v>0.770452979085074</v>
+        <v>0.8535249644440821</v>
       </c>
       <c r="I8">
-        <v>0.850407710178867</v>
+        <v>0.04433511045571774</v>
       </c>
       <c r="J8">
-        <v>0.8635975609756098</v>
+        <v>0.8218095370018286</v>
       </c>
       <c r="K8">
-        <v>0.05137659002159779</v>
+        <v>0.8852403918863356</v>
       </c>
       <c r="L8">
-        <v>0.8268449624975281</v>
+        <v>0.8678494623655915</v>
       </c>
       <c r="M8">
-        <v>0.9003501594536915</v>
+        <v>0.08403997614818053</v>
       </c>
       <c r="N8">
-        <v>0.8348508423921688</v>
+        <v>0.8077308850488951</v>
       </c>
       <c r="O8">
-        <v>0.04186417189914927</v>
+        <v>0.9279680396822878</v>
       </c>
       <c r="P8">
-        <v>0.8049030179106293</v>
+        <v>0.8571000910727555</v>
       </c>
       <c r="Q8">
-        <v>0.8647986668737082</v>
+        <v>0.03332981976642756</v>
       </c>
       <c r="R8">
-        <v>0.8813594789356985</v>
+        <v>0.8332573743274949</v>
       </c>
       <c r="S8">
-        <v>0.03120498782968092</v>
+        <v>0.8809428078180161</v>
       </c>
       <c r="T8">
-        <v>0.8590367753904542</v>
+        <v>0.90962688172043</v>
       </c>
       <c r="U8">
-        <v>0.9036821824809429</v>
+        <v>0.03359504653220673</v>
+      </c>
+      <c r="V8">
+        <v>0.8855944331766163</v>
+      </c>
+      <c r="W8">
+        <v>0.9336593302642437</v>
       </c>
     </row>
-    <row r="9" spans="1:21">
+    <row r="9" spans="1:23">
       <c r="A9" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B9">
-        <v>0.797741577193632</v>
-      </c>
-      <c r="C9">
-        <v>0.05828212980716496</v>
+        <v>10</v>
+      </c>
+      <c r="C9" t="s">
+        <v>31</v>
       </c>
       <c r="D9">
-        <v>0.7560490531403677</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="E9">
-        <v>0.8394341012468963</v>
+        <v>0.0415051967715489</v>
       </c>
       <c r="F9">
-        <v>0.7938777572085139</v>
+        <v>0.7903089708550676</v>
       </c>
       <c r="G9">
-        <v>0.05900488554940816</v>
+        <v>0.8496910291449326</v>
       </c>
       <c r="H9">
-        <v>0.7516682048436932</v>
+        <v>0.8259268365924045</v>
       </c>
       <c r="I9">
-        <v>0.8360873095733347</v>
+        <v>0.06167819453557855</v>
       </c>
       <c r="J9">
-        <v>0.8585975609756099</v>
+        <v>0.7818049141824861</v>
       </c>
       <c r="K9">
-        <v>0.06645405940971461</v>
+        <v>0.8700487590023229</v>
       </c>
       <c r="L9">
-        <v>0.8110591906459111</v>
+        <v>0.8646236559139785</v>
       </c>
       <c r="M9">
-        <v>0.9061359313053087</v>
+        <v>0.07287091829150583</v>
       </c>
       <c r="N9">
-        <v>0.8236361846538737</v>
+        <v>0.8124949412684378</v>
       </c>
       <c r="O9">
-        <v>0.05212671792437854</v>
+        <v>0.9167523705595192</v>
       </c>
       <c r="P9">
-        <v>0.7863469770001633</v>
+        <v>0.8413425418562988</v>
       </c>
       <c r="Q9">
-        <v>0.860925392307584</v>
+        <v>0.03675959285973909</v>
       </c>
       <c r="R9">
-        <v>0.8808573540280857</v>
+        <v>0.8150463132427648</v>
       </c>
       <c r="S9">
-        <v>0.028728117518753</v>
+        <v>0.8676387704698327</v>
       </c>
       <c r="T9">
-        <v>0.8603064967650011</v>
+        <v>0.9132112903225806</v>
       </c>
       <c r="U9">
-        <v>0.9014082112911703</v>
+        <v>0.02077367038561231</v>
+      </c>
+      <c r="V9">
+        <v>0.8983507017495074</v>
+      </c>
+      <c r="W9">
+        <v>0.9280718788956539</v>
       </c>
     </row>
   </sheetData>
